--- a/ams/cases/5bus/pjm5bus_demo.xlsx
+++ b/ams/cases/5bus/pjm5bus_demo.xlsx
@@ -21,10 +21,10 @@
     <sheet name="Line" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Area" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="Zone" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="EDTSlot" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="EDSlot" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="EDSlotLoad" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="EDSlotGen" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="UCTSlot" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="UCSlot" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="UCSlotLoad" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="SFR" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="SFRCost" sheetId="21" state="visible" r:id="rId21"/>

--- a/ams/cases/5bus/pjm5bus_demo.xlsx
+++ b/ams/cases/5bus/pjm5bus_demo.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Load factor in EDTSlot and UCTSlot sourced from PJM 5-minutes load on August 30, 2023</t>
+          <t>Load factor in EDSlotLoad and UCSlotLoad sourced from PJM 5-minutes load on August 30, 2023</t>
         </is>
       </c>
     </row>
